--- a/inasistencias-7A/Alumnos-7A.xlsx
+++ b/inasistencias-7A/Alumnos-7A.xlsx
@@ -5,18 +5,18 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="notas" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="1-uml" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="2-DA" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="2-recup" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="3-DCU" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="4-java Gen" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="1-Recup" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="positivos" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="positivos" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="1-uml" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="2-DA" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="2-recup" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="3-DCU" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="4-java Gen" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="1-Recup" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="5-redes" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="216">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -67,6 +67,18 @@
     <t xml:space="preserve">nota presentes</t>
   </si>
   <si>
+    <t xml:space="preserve">media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santino</t>
   </si>
   <si>
@@ -142,9 +154,6 @@
     <t xml:space="preserve">olimpiadas</t>
   </si>
   <si>
-    <t xml:space="preserve">O</t>
-  </si>
-  <si>
     <t xml:space="preserve">olimpiada</t>
   </si>
   <si>
@@ -277,6 +286,21 @@
     <t xml:space="preserve">Repositorio</t>
   </si>
   <si>
+    <t xml:space="preserve">1-entorno de desarrollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-respositorio de objesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-asistencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asis+posi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total alumnos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finalizado</t>
   </si>
   <si>
@@ -599,9 +623,6 @@
   </si>
   <si>
     <t xml:space="preserve">5 minutos 42 segundos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total alumnos</t>
   </si>
   <si>
     <t xml:space="preserve">4 minutos 43 segundos</t>
@@ -701,6 +722,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
         <bgColor rgb="FFFF9800"/>
       </patternFill>
@@ -709,12 +736,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9800"/>
         <bgColor rgb="FFFFC107"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -759,12 +780,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -780,11 +805,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -792,11 +813,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,11 +845,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -825,7 +862,50 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -906,7 +986,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1039,7 +1119,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AP21"/>
   <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -1049,13 +1129,15 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="11.17"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="11" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="21" style="1" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="34" min="22" style="1" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="35" style="2" width="8.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
       <c r="V1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,48 +1147,54 @@
       <c r="X1" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="AO1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP1" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>45800</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>45807</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>45814</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>45821</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>45842</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="O2" s="1" t="s">
@@ -1127,73 +1215,100 @@
       <c r="T2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>45856</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="X2" s="3" t="n">
+      <c r="X2" s="4" t="n">
         <v>45898</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Y2" s="4" t="n">
         <v>45905</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="3" t="n">
+      <c r="AA2" s="4" t="n">
         <v>45926</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" s="4" t="n">
         <v>45933</v>
       </c>
-      <c r="AD2" s="3" t="n">
+      <c r="AD2" s="4" t="n">
         <v>45947</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AE2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF2" s="6" t="n">
+      <c r="AF2" s="4" t="n">
         <v>45954</v>
+      </c>
+      <c r="AG2" s="4" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="6" t="n">
+        <v>45989</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">COUNTIF(E3:N3,"P")</f>
@@ -1215,71 +1330,96 @@
         <f aca="false">ROUND(P3+Q3+R3/2+S3/4+0,0)</f>
         <v>6</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="5" t="n">
         <f aca="false">ROUND(T3*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z3" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB3" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="AE3" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="AF3" s="5" t="s">
-        <v>16</v>
+      <c r="AF3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH3" s="7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AI3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ3" s="3" t="n">
+        <f aca="false">COUNTIF(V3:AG3,"P")</f>
+        <v>1</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <f aca="false">COUNTIF(V3:AG3,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="AL3" s="3" t="n">
+        <f aca="false">COUNTIF(V3:AG3,"T")</f>
+        <v>3</v>
+      </c>
+      <c r="AM3" s="9" t="n">
+        <f aca="false">ROUND((AJ3+AK3/2+AL3/4)*10/8,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">COUNTIF(E4:N4,"P")</f>
@@ -1301,68 +1441,90 @@
         <f aca="false">ROUND(P4+Q4+R4/2,0)</f>
         <v>6</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="5" t="n">
         <f aca="false">ROUND(T4*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF4" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <f aca="false">COUNTIF(V4:AG4,"P")</f>
+        <v>8</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <f aca="false">COUNTIF(V4:AG4,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <f aca="false">COUNTIF(V4:AG4,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="9" t="n">
+        <f aca="false">ROUND((AJ4+AK4/2+AL4/4)*10/8,0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0.631944444444444</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P5" s="1" t="n">
         <f aca="false">COUNTIF(E5:N5,"P")</f>
@@ -1384,62 +1546,84 @@
         <f aca="false">ROUND(P5+Q5+R5/2,0)</f>
         <v>0</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="5" t="n">
         <f aca="false">ROUND(T5*10/$W$1,0)</f>
         <v>0</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF5" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <f aca="false">COUNTIF(V5:AG5,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <f aca="false">COUNTIF(V5:AG5,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <f aca="false">COUNTIF(V5:AG5,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM5" s="9" t="n">
+        <f aca="false">ROUND((AJ5+AK5/2+AL5/4)*10/8,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">COUNTIF(E6:N6,"P")</f>
@@ -1461,65 +1645,87 @@
         <f aca="false">ROUND(P6+Q6+R6/2,0)</f>
         <v>3</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="5" t="n">
         <f aca="false">ROUND(T6*10/$W$1,0)</f>
         <v>5</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="AE6" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="AF6" s="5" t="s">
-        <v>15</v>
+      <c r="AF6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <f aca="false">COUNTIF(V6:AG6,"P")</f>
+        <v>3</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <f aca="false">COUNTIF(V6:AG6,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <f aca="false">COUNTIF(V6:AG6,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="9" t="n">
+        <f aca="false">ROUND((AJ6+AK6/2+AL6/4)*10/8,0)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">COUNTIF(E7:N7,"P")</f>
@@ -1541,68 +1747,90 @@
         <f aca="false">ROUND(P7+Q7+R7/2,0)</f>
         <v>5</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="5" t="n">
         <f aca="false">ROUND(T7*10/$W$1,0)</f>
         <v>8</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF7" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ7" s="3" t="n">
+        <f aca="false">COUNTIF(V7:AG7,"P")</f>
+        <v>6</v>
+      </c>
+      <c r="AK7" s="3" t="n">
+        <f aca="false">COUNTIF(V7:AG7,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="3" t="n">
+        <f aca="false">COUNTIF(V7:AG7,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="9" t="n">
+        <f aca="false">ROUND((AJ7+AK7/2+AL7/4)*10/8,0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>0.604166666666667</v>
@@ -1627,77 +1855,99 @@
         <f aca="false">ROUND(P8+Q8+R8/2,0)</f>
         <v>4</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="5" t="n">
         <f aca="false">ROUND(T8*10/$W$1,0)</f>
         <v>7</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="W8" s="7" t="n">
         <v>0.625</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z8" s="7" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB8" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF8" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="AD8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <f aca="false">COUNTIF(V8:AG8,"P")</f>
+        <v>3</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <f aca="false">COUNTIF(V8:AG8,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="AL8" s="3" t="n">
+        <f aca="false">COUNTIF(V8:AG8,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="AM8" s="9" t="n">
+        <f aca="false">ROUND((AJ8+AK8/2+AL8/4)*10/8,0)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P9" s="1" t="n">
         <f aca="false">COUNTIF(E9:N9,"P")</f>
@@ -1719,63 +1969,90 @@
         <f aca="false">ROUND(P9+Q9+R9/2,0)</f>
         <v>2</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="5" t="n">
         <f aca="false">ROUND(T9*10/$W$1,0)</f>
         <v>3</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF9" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ9" s="3" t="n">
+        <f aca="false">COUNTIF(V9:AG9,"P")</f>
+        <v>1</v>
+      </c>
+      <c r="AK9" s="3" t="n">
+        <f aca="false">COUNTIF(V9:AG9,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="3" t="n">
+        <f aca="false">COUNTIF(V9:AG9,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="9" t="n">
+        <f aca="false">ROUND((AJ9+AK9/2+AL9/4)*10/8,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="11" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O10" s="1"/>
       <c r="P10" s="1" t="n">
         <f aca="false">COUNTIF(E10:N10,"P")</f>
         <v>6</v>
@@ -1796,145 +2073,210 @@
         <f aca="false">ROUND(P10+Q10+R10/2,0)</f>
         <v>6</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="5" t="n">
         <f aca="false">ROUND(T10*10/$W$1,0)</f>
         <v>10</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="W10" s="1"/>
       <c r="X10" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB10" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF10" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH10" s="7" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="AI10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <f aca="false">COUNTIF(V10:AG10,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <f aca="false">COUNTIF(V10:AG10,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="3" t="n">
+        <f aca="false">COUNTIF(V10:AG10,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="AM10" s="9" t="n">
+        <f aca="false">ROUND((AJ10+AK10/2+AL10/4)*10/8,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AN10" s="0"/>
+      <c r="AO10" s="0"/>
+      <c r="AP10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="7" t="n">
+      <c r="B11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>0.625</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P11" s="1" t="n">
+      <c r="N11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2" t="n">
         <f aca="false">COUNTIF(E11:N11,"P")</f>
         <v>3</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="Q11" s="2" t="n">
         <f aca="false">COUNTIF(E11:N11,"C")</f>
         <v>0</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11" s="2" t="n">
         <f aca="false">COUNTIF(E11:N11,"M")</f>
         <v>1</v>
       </c>
-      <c r="S11" s="1" t="n">
+      <c r="S11" s="2" t="n">
         <f aca="false">COUNTIF(E11:N11,"T")</f>
         <v>0</v>
       </c>
-      <c r="T11" s="1" t="n">
+      <c r="T11" s="2" t="n">
         <f aca="false">ROUND(P11+Q11+R11/2,0)</f>
         <v>4</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="12" t="n">
         <f aca="false">ROUND(T11*10/$W$1,0)</f>
         <v>7</v>
       </c>
-      <c r="V11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="V11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE11" s="2"/>
+      <c r="AF11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH11" s="2"/>
+      <c r="AI11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ11" s="10" t="n">
+        <f aca="false">COUNTIF(V11:AG11,"P")</f>
+        <v>8</v>
+      </c>
+      <c r="AK11" s="10" t="n">
+        <f aca="false">COUNTIF(V11:AG11,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10" t="n">
+        <f aca="false">COUNTIF(V11:AG11,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="13" t="n">
+        <f aca="false">ROUND((AJ11+AK11/2+AL11/4)*10/8,0)</f>
+        <v>10</v>
+      </c>
+      <c r="AN11" s="11"/>
+      <c r="AO11" s="11"/>
+      <c r="AP11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>50</v>
+      <c r="B12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P12" s="1" t="n">
         <f aca="false">COUNTIF(E12:N12,"P")</f>
@@ -1956,65 +2298,87 @@
         <f aca="false">ROUND(P12+Q12+R12/2,0)</f>
         <v>0</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="5" t="n">
         <f aca="false">ROUND(T12*10/$W$1,0)</f>
         <v>0</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF12" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ12" s="3" t="n">
+        <f aca="false">COUNTIF(V12:AG12,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <f aca="false">COUNTIF(V12:AG12,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <f aca="false">COUNTIF(V12:AG12,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="9" t="n">
+        <f aca="false">ROUND((AJ12+AK12/2+AL12/4)*10/8,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>53</v>
+      <c r="B13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P13" s="1" t="n">
         <f aca="false">COUNTIF(E13:N13,"P")</f>
@@ -2036,65 +2400,87 @@
         <f aca="false">ROUND(P13+Q13+R13/2,0)</f>
         <v>5</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="U13" s="5" t="n">
         <f aca="false">ROUND(T13*10/$W$1,0)</f>
         <v>8</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF13" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="AD13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ13" s="3" t="n">
+        <f aca="false">COUNTIF(V13:AG13,"P")</f>
+        <v>7</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <f aca="false">COUNTIF(V13:AG13,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3" t="n">
+        <f aca="false">COUNTIF(V13:AG13,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="9" t="n">
+        <f aca="false">ROUND((AJ13+AK13/2+AL13/4)*10/8,0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>56</v>
+      <c r="B14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P14" s="1" t="n">
         <f aca="false">COUNTIF(E14:N14,"P")</f>
@@ -2116,65 +2502,87 @@
         <f aca="false">ROUND(P14+Q14+R14/2,0)</f>
         <v>4</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="5" t="n">
         <f aca="false">ROUND(T14*10/$W$1,0)</f>
         <v>7</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Z14" s="7" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF14" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ14" s="3" t="n">
+        <f aca="false">COUNTIF(V14:AG14,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <f aca="false">COUNTIF(V14:AG14,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="n">
+        <f aca="false">COUNTIF(V14:AG14,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="9" t="n">
+        <f aca="false">ROUND((AJ14+AK14/2+AL14/4)*10/8,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>59</v>
+      <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P15" s="1" t="n">
         <f aca="false">COUNTIF(E15:N15,"P")</f>
@@ -2196,65 +2604,87 @@
         <f aca="false">ROUND(P15+Q15+R15/2,0)</f>
         <v>2</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="U15" s="5" t="n">
         <f aca="false">ROUND(T15*10/$W$1,0)</f>
         <v>3</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="7" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF15" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ15" s="3" t="n">
+        <f aca="false">COUNTIF(V15:AG15,"P")</f>
+        <v>2</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <f aca="false">COUNTIF(V15:AG15,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3" t="n">
+        <f aca="false">COUNTIF(V15:AG15,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="AM15" s="9" t="n">
+        <f aca="false">ROUND((AJ15+AK15/2+AL15/4)*10/8,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>62</v>
+      <c r="B16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>0.645833333333333</v>
@@ -2279,33 +2709,55 @@
         <f aca="false">ROUND(P16+Q16+R16/2,0)</f>
         <v>4</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="U16" s="5" t="n">
         <f aca="false">ROUND(T16*10/$W$1,0)</f>
         <v>7</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Z16" s="7" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF16" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ16" s="3" t="n">
+        <f aca="false">COUNTIF(V16:AG16,"P")</f>
+        <v>4</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <f aca="false">COUNTIF(V16:AG16,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <f aca="false">COUNTIF(V16:AG16,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="9" t="n">
+        <f aca="false">ROUND((AJ16+AK16/2+AL16/4)*10/8,0)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2357,23 +2809,27 @@
       </c>
       <c r="AC17" s="1" t="n">
         <f aca="false">COUNTIF(AC3:AC16,"P")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD16,"P")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF17" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF16,"P")</f>
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG16,"P")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G18" s="1" t="n">
         <f aca="false">COUNTIF(G3:G16,"T")</f>
@@ -2407,6 +2863,10 @@
         <f aca="false">COUNTIF(AF3:AF16,"M")</f>
         <v>0</v>
       </c>
+      <c r="AG18" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG16,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
@@ -2440,24 +2900,31 @@
         <f aca="false">COUNTIF(AF3:AF16,"T")</f>
         <v>0</v>
       </c>
+      <c r="AG19" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG16,"T")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC20" s="1"/>
+        <v>40</v>
+      </c>
       <c r="AD20" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD16,"o")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF16,"o")</f>
         <v>0</v>
       </c>
+      <c r="AG20" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG16,"o")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="V21" s="1" t="n">
         <f aca="false">SUM(V17:V19)</f>
@@ -2477,7 +2944,7 @@
       </c>
       <c r="AC21" s="1" t="n">
         <f aca="false">SUM(AC17:AC19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD21" s="1" t="n">
         <f aca="false">SUM(AD17:AD20)</f>
@@ -2485,10 +2952,26 @@
       </c>
       <c r="AF21" s="1" t="n">
         <f aca="false">SUM(AF17:AF20)</f>
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="AG21" s="1" t="n">
+        <f aca="false">SUM(AG17:AG20)</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="AM3:AM16">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2518,27 +3001,27 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -2551,17 +3034,17 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -2580,13 +3063,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>5</v>
@@ -2594,13 +3077,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>5</v>
@@ -2608,13 +3091,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>4</v>
@@ -2622,13 +3105,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3</v>
@@ -2636,13 +3119,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
@@ -2650,13 +3133,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -2666,8 +3149,8 @@
       <c r="A10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>23</v>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1</v>
@@ -2680,17 +3163,17 @@
       <c r="A11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>27</v>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8</v>
@@ -2703,17 +3186,17 @@
       <c r="A12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -2726,17 +3209,17 @@
       <c r="A13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>33</v>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -2749,17 +3232,17 @@
       <c r="A14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>40</v>
+      <c r="B14" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -2772,17 +3255,17 @@
       <c r="A15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>43</v>
+      <c r="B15" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -2795,8 +3278,8 @@
       <c r="A16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
+      <c r="B16" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -2809,8 +3292,8 @@
       <c r="A17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>49</v>
+      <c r="B17" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -2823,17 +3306,17 @@
       <c r="A18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>52</v>
+      <c r="B18" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -2852,13 +3335,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -2866,13 +3349,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>6</v>
@@ -2880,13 +3363,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
@@ -2896,17 +3379,17 @@
       <c r="A22" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>55</v>
+      <c r="B22" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -2919,17 +3402,17 @@
       <c r="A23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>58</v>
+      <c r="B23" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -2942,28 +3425,28 @@
       <c r="A24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
+      <c r="B24" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H25" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="I25" s="1" t="n">
         <f aca="false">COUNTIF(I2:I24,"&gt;0")</f>
@@ -2986,7 +3469,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr defaultColWidth="9.61328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -2995,94 +3478,113 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="12" style="1" width="9.52"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="11.44"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="16" style="1" width="9.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="1" width="14.62"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="20" style="1" width="9.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T1" s="4" t="n">
+        <v>45877</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="Z1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="T1" s="3" t="n">
-        <v>45877</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="8" t="n">
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="15" t="n">
         <v>45855</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" s="17" t="n">
         <v>45821</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" s="17" t="n">
         <v>45849</v>
       </c>
       <c r="J2" s="1" t="n">
@@ -3100,7 +3602,7 @@
         <f aca="false">IF(L2&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N2" s="14" t="n">
         <v>3</v>
       </c>
       <c r="O2" s="1" t="n">
@@ -3115,11 +3617,31 @@
       <c r="R2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S2" s="12" t="n">
+      <c r="S2" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N2:O2,L2),0)</f>
         <v>7</v>
       </c>
+      <c r="U2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" s="1" t="n">
+        <f aca="false">X2+Y2/2</f>
+        <v>5.5</v>
+      </c>
+      <c r="AA2" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V2:W2,Z2),0)&gt;10,10,ROUND(AVERAGE(V2:W2,Z2),0))</f>
         <v>7</v>
       </c>
     </row>
@@ -3127,8 +3649,8 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>7</v>
@@ -3172,11 +3694,31 @@
       <c r="R3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S3" s="12" t="n">
+      <c r="S3" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N3:O3,L3),0)</f>
         <v>8</v>
       </c>
+      <c r="U3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <f aca="false">X3+Y3/2</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA3" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V3:W3,Z3),0)&gt;10,10,ROUND(AVERAGE(V3:W3,Z3),0))</f>
         <v>7</v>
       </c>
     </row>
@@ -3184,8 +3726,8 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -3229,14 +3771,34 @@
       <c r="R4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S4" s="12" t="n">
+      <c r="S4" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N4:O4,L4),0)</f>
         <v>1</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <f aca="false">X4+Y4/2</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V4:W4,Z4),0)&gt;10,10,ROUND(AVERAGE(V4:W4,Z4),0))</f>
         <v>1</v>
       </c>
     </row>
@@ -3244,19 +3806,19 @@
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="8" t="n">
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="15" t="n">
         <v>45887</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="15" t="n">
         <v>45856</v>
       </c>
       <c r="G5" s="1" t="n">
@@ -3295,11 +3857,31 @@
       <c r="R5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="S5" s="12" t="n">
+      <c r="S5" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N5:O5,L5),0)</f>
         <v>7</v>
       </c>
+      <c r="U5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <f aca="false">X5+Y5/2</f>
+        <v>5.5</v>
+      </c>
+      <c r="AA5" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V5:W5,Z5),0)&gt;10,10,ROUND(AVERAGE(V5:W5,Z5),0))</f>
         <v>7</v>
       </c>
     </row>
@@ -3307,8 +3889,8 @@
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>8</v>
@@ -3352,11 +3934,31 @@
       <c r="R6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N6:O6,L6),0)</f>
         <v>8</v>
       </c>
+      <c r="U6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="W6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <f aca="false">X6+Y6/2</f>
+        <v>8.5</v>
+      </c>
+      <c r="AA6" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V6:W6,Z6),0)&gt;10,10,ROUND(AVERAGE(V6:W6,Z6),0))</f>
         <v>10</v>
       </c>
     </row>
@@ -3364,8 +3966,8 @@
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>10</v>
@@ -3409,20 +4011,40 @@
       <c r="R7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S7" s="12" t="n">
+      <c r="S7" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N7:O7,L7),0)</f>
         <v>9</v>
       </c>
+      <c r="U7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="W7" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <f aca="false">X7+Y7/2</f>
+        <v>34</v>
+      </c>
+      <c r="AA7" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V7:W7,Z7),0)&gt;10,10,ROUND(AVERAGE(V7:W7,Z7),0))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>1</v>
@@ -3466,23 +4088,43 @@
       <c r="R8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S8" s="12" t="n">
+      <c r="S8" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N8:O8,L8),0)</f>
         <v>5</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <f aca="false">X8+Y8/2</f>
+        <v>5.5</v>
+      </c>
+      <c r="AA8" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V8:W8,Z8),0)&gt;10,10,ROUND(AVERAGE(V8:W8,Z8),0))</f>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>43</v>
+      <c r="B9" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>7</v>
@@ -3526,20 +4168,40 @@
       <c r="R9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N9:O9,L9),0)</f>
         <v>9</v>
       </c>
+      <c r="U9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W9" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <f aca="false">X9+Y9/2</f>
+        <v>15.5</v>
+      </c>
+      <c r="AA9" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V9:W9,Z9),0)&gt;10,10,ROUND(AVERAGE(V9:W9,Z9),0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
+      <c r="B10" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>8</v>
@@ -3550,10 +4212,10 @@
       <c r="G10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="15" t="n">
         <v>45855</v>
       </c>
       <c r="J10" s="1" t="n">
@@ -3571,7 +4233,7 @@
         <f aca="false">IF(L10&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="14" t="n">
         <v>5</v>
       </c>
       <c r="O10" s="1" t="n">
@@ -3586,20 +4248,40 @@
       <c r="R10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="12" t="n">
+      <c r="S10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N10:O10,L10),0)</f>
         <v>7</v>
       </c>
+      <c r="U10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W10" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <f aca="false">X10+Y10/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA10" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V10:W10,Z10),0)&gt;10,10,ROUND(AVERAGE(V10:W10,Z10),0))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>49</v>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>1</v>
@@ -3643,23 +4325,43 @@
       <c r="R11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N11:O11,L11),0)</f>
         <v>1</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <f aca="false">X11+Y11/2</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V11:W11,Z11),0)&gt;10,10,ROUND(AVERAGE(V11:W11,Z11),0))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>52</v>
+      <c r="B12" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>9</v>
@@ -3703,11 +4405,31 @@
       <c r="R12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S12" s="12" t="n">
+      <c r="S12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N12:O12,L12),0)</f>
         <v>8</v>
       </c>
+      <c r="U12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="W12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <f aca="false">X12+Y12/2</f>
+        <v>39.5</v>
+      </c>
+      <c r="AA12" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V12:W12,Z12),0)&gt;10,10,ROUND(AVERAGE(V12:W12,Z12),0))</f>
         <v>10</v>
       </c>
     </row>
@@ -3715,16 +4437,16 @@
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>55</v>
+      <c r="B13" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="17" t="n">
         <v>45821</v>
       </c>
       <c r="G13" s="1" t="n">
@@ -3763,31 +4485,51 @@
       <c r="R13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S13" s="12" t="n">
+      <c r="S13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N13:O13,L13),0)</f>
         <v>7</v>
       </c>
+      <c r="U13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W13" s="1" t="n">
         <v>7</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <f aca="false">X13+Y13/2</f>
+        <v>9.5</v>
+      </c>
+      <c r="AA13" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V13:W13,Z13),0)&gt;10,10,ROUND(AVERAGE(V13:W13,Z13),0))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>45758</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="E14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>45758</v>
       </c>
       <c r="G14" s="1" t="n">
@@ -3826,11 +4568,31 @@
       <c r="R14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N14:O14,L14),0)</f>
         <v>7</v>
       </c>
+      <c r="U14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>7</v>
+      </c>
       <c r="W14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <f aca="false">X14+Y14/2</f>
+        <v>6</v>
+      </c>
+      <c r="AA14" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V14:W14,Z14),0)&gt;10,10,ROUND(AVERAGE(V14:W14,Z14),0))</f>
         <v>7</v>
       </c>
     </row>
@@ -3838,8 +4600,8 @@
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
+      <c r="B15" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>10</v>
@@ -3850,10 +4612,10 @@
       <c r="G15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="9" t="n">
+      <c r="H15" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="15" t="n">
         <v>45856</v>
       </c>
       <c r="J15" s="1" t="n">
@@ -3886,24 +4648,56 @@
       <c r="R15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(N15:O15,L15),0)</f>
         <v>9</v>
       </c>
+      <c r="U15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="W15" s="1" t="n">
         <v>7</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <f aca="false">X15+Y15/2</f>
+        <v>7</v>
+      </c>
+      <c r="AA15" s="9" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V15:W15,Z15),0)&gt;10,10,ROUND(AVERAGE(V15:W15,Z15),0))</f>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="S2:S15">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA15">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3922,243 +4716,254 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="9.61328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="G1:L16"/>
+  <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>84</v>
+      <c r="I1" s="4" t="n">
+        <v>45737</v>
+      </c>
+      <c r="J1" s="4" t="n">
+        <v>45751</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="G2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <f aca="false">I2+J2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <f aca="false">I3+J3</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <f aca="false">I4+J4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <f aca="false">I5+J5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <f aca="false">I6+J6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <f aca="false">I7+J7</f>
+        <v>60</v>
+      </c>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <f aca="false">I8+J8</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <f aca="false">I9+J9</f>
+        <v>25</v>
+      </c>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <f aca="false">I10+J10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <f aca="false">I11+J11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <f aca="false">I12+J12</f>
+        <v>63</v>
+      </c>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <f aca="false">I13+J13</f>
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <f aca="false">I14+J14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="K15" s="1" t="n">
+        <f aca="false">I15+J15</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <f aca="false">COUNTIF(I2:I15,"&gt;0")</f>
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>10</v>
+      <c r="J16" s="1" t="n">
+        <f aca="false">COUNTIF(J2:J15,"&gt;0")</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4173,6 +4978,261 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9.61328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.57"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4192,30 +5252,30 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -4228,17 +5288,17 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -4257,13 +5317,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -4271,13 +5331,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -4285,13 +5345,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>6</v>
@@ -4299,13 +5359,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>4</v>
@@ -4315,8 +5375,8 @@
       <c r="A8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -4329,8 +5389,8 @@
       <c r="A9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -4343,17 +5403,17 @@
       <c r="A10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>30</v>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -4366,17 +5426,17 @@
       <c r="A11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>9</v>
@@ -4389,8 +5449,8 @@
       <c r="A12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>40</v>
+      <c r="B12" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -4403,17 +5463,17 @@
       <c r="A13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>43</v>
+      <c r="B13" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -4432,13 +5492,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>5</v>
@@ -4448,17 +5508,17 @@
       <c r="A15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>46</v>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -4471,8 +5531,8 @@
       <c r="A16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>49</v>
+      <c r="B16" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -4485,17 +5545,17 @@
       <c r="A17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>52</v>
+      <c r="B17" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -4514,13 +5574,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>5</v>
@@ -4530,8 +5590,8 @@
       <c r="A19" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>55</v>
+      <c r="B19" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -4544,8 +5604,8 @@
       <c r="A20" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>58</v>
+      <c r="B20" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -4558,17 +5618,17 @@
       <c r="A21" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>61</v>
+      <c r="B21" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -4588,7 +5648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4606,51 +5666,51 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -4694,7 +5754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4714,39 +5774,39 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -4759,17 +5819,17 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -4788,13 +5848,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -4804,8 +5864,8 @@
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -4818,17 +5878,17 @@
       <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -4841,17 +5901,17 @@
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -4870,13 +5930,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>8</v>
@@ -4886,17 +5946,17 @@
       <c r="A10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>33</v>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -4915,13 +5975,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -4929,13 +5989,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
@@ -4945,17 +6005,17 @@
       <c r="A13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>40</v>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -4974,13 +6034,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -4988,13 +6048,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>1</v>
@@ -5004,17 +6064,17 @@
       <c r="A16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>43</v>
+      <c r="B16" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -5033,13 +6093,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -5047,13 +6107,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>3</v>
@@ -5063,17 +6123,17 @@
       <c r="A19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>46</v>
+      <c r="B19" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -5092,13 +6152,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -5108,8 +6168,8 @@
       <c r="A21" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>49</v>
+      <c r="B21" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -5122,17 +6182,17 @@
       <c r="A22" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
+      <c r="B22" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -5151,13 +6211,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>7</v>
@@ -5167,17 +6227,17 @@
       <c r="A24" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>55</v>
+      <c r="B24" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -5196,13 +6256,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -5212,17 +6272,17 @@
       <c r="A26" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>58</v>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -5235,17 +6295,17 @@
       <c r="A27" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>61</v>
+      <c r="B27" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -5274,7 +6334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5293,30 +6353,30 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -5329,17 +6389,17 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -5358,13 +6418,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -5374,17 +6434,17 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -5397,17 +6457,17 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -5420,17 +6480,17 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -5443,17 +6503,17 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -5466,8 +6526,8 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -5480,17 +6540,17 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
+      <c r="B10" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -5503,8 +6563,8 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
+      <c r="B11" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -5517,8 +6577,8 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>49</v>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -5531,17 +6591,17 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>52</v>
+      <c r="B13" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -5554,17 +6614,17 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>55</v>
+      <c r="B14" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -5577,17 +6637,17 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>58</v>
+      <c r="B15" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -5600,8 +6660,8 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>61</v>
+      <c r="B16" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -5630,7 +6690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5649,51 +6709,51 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -5724,263 +6784,6 @@
       </c>
       <c r="M2" s="1" t="n">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="G1:K16"/>
-  <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.45"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="3" t="n">
-        <v>45737</v>
-      </c>
-      <c r="J1" s="3" t="n">
-        <v>45751</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <f aca="false">I2+J2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <f aca="false">I3+J3</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <f aca="false">I4+J4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <f aca="false">I5+J5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <f aca="false">I6+J6</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <f aca="false">I7+J7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <f aca="false">I8+J8</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <f aca="false">I9+J9</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <f aca="false">I10+J10</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <f aca="false">I11+J11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <f aca="false">I12+J12</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <f aca="false">I13+J13</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <f aca="false">I14+J14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <f aca="false">I15+J15</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H16" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <f aca="false">COUNTIF(I2:I15,"&gt;0")</f>
-        <v>6</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <f aca="false">COUNTIF(J2:J15,"&gt;0")</f>
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/inasistencias-7A/Alumnos-7A.xlsx
+++ b/inasistencias-7A/Alumnos-7A.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="217">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -73,12 +73,6 @@
     <t xml:space="preserve">nota</t>
   </si>
   <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santino</t>
   </si>
   <si>
@@ -296,6 +290,15 @@
   </si>
   <si>
     <t xml:space="preserve">asis+posi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nota </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diciembrre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobado</t>
   </si>
   <si>
     <t xml:space="preserve">total alumnos</t>
@@ -780,7 +783,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -809,6 +812,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -825,7 +832,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -834,6 +841,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -853,6 +868,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -862,7 +885,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -943,6 +966,36 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -1129,9 +1182,9 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="11.17"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="11" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="8.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="34" min="22" style="1" width="8.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="35" style="2" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="21" style="1" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="35" style="2" width="8.77"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="39" min="36" style="0" width="8.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1147,12 +1200,8 @@
       <c r="X1" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AO1" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP1" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -1272,43 +1321,42 @@
       <c r="AM2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AN2" s="7" t="n">
+        <v>45996</v>
+      </c>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AP2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P3" s="1" t="n">
         <f aca="false">COUNTIF(E3:N3,"P")</f>
@@ -1335,43 +1383,43 @@
         <v>10</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Z3" s="8" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB3" s="8" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z3" s="7" t="n">
+      <c r="AE3" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="AA3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB3" s="7" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE3" s="7" t="n">
-        <v>0.645833333333333</v>
-      </c>
       <c r="AF3" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH3" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH3" s="8" t="n">
         <v>0.625</v>
       </c>
-      <c r="AI3" s="8" t="s">
-        <v>20</v>
+      <c r="AI3" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <f aca="false">COUNTIF(V3:AG3,"P")</f>
@@ -1385,41 +1433,41 @@
         <f aca="false">COUNTIF(V3:AG3,"T")</f>
         <v>3</v>
       </c>
-      <c r="AM3" s="9" t="n">
+      <c r="AM3" s="10" t="n">
         <f aca="false">ROUND((AJ3+AK3/2+AL3/4)*10/8,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P4" s="1" t="n">
         <f aca="false">COUNTIF(E4:N4,"P")</f>
@@ -1446,31 +1494,31 @@
         <v>10</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI4" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ4" s="3" t="n">
         <f aca="false">COUNTIF(V4:AG4,"P")</f>
@@ -1484,146 +1532,157 @@
         <f aca="false">COUNTIF(V4:AG4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM4" s="9" t="n">
+      <c r="AM4" s="10" t="n">
         <f aca="false">ROUND((AJ4+AK4/2+AL4/4)*10/8,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    <row r="5" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0.631944444444444</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0.631944444444444</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" s="1" t="n">
+      <c r="K5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2" t="n">
         <f aca="false">COUNTIF(E5:N5,"P")</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="Q5" s="2" t="n">
         <f aca="false">COUNTIF(E5:N5,"C")</f>
         <v>0</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <f aca="false">COUNTIF(E5:N5,"M")</f>
         <v>0</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="S5" s="2" t="n">
         <f aca="false">COUNTIF(E5:N5,"T")</f>
         <v>1</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="T5" s="2" t="n">
         <f aca="false">ROUND(P5+Q5+R5/2,0)</f>
         <v>0</v>
       </c>
-      <c r="U5" s="5" t="n">
+      <c r="U5" s="13" t="n">
         <f aca="false">ROUND(T5*10/$W$1,0)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ5" s="3" t="n">
+      <c r="V5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ5" s="11" t="n">
         <f aca="false">COUNTIF(V5:AG5,"P")</f>
         <v>0</v>
       </c>
-      <c r="AK5" s="3" t="n">
+      <c r="AK5" s="11" t="n">
         <f aca="false">COUNTIF(V5:AG5,"M")</f>
         <v>0</v>
       </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AL5" s="11" t="n">
         <f aca="false">COUNTIF(V5:AG5,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="9" t="n">
+      <c r="AM5" s="14" t="n">
         <f aca="false">ROUND((AJ5+AK5/2+AL5/4)*10/8,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN5" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P6" s="1" t="n">
         <f aca="false">COUNTIF(E6:N6,"P")</f>
@@ -1650,34 +1709,34 @@
         <v>5</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE6" s="7" t="n">
+      <c r="AE6" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <f aca="false">COUNTIF(V6:AG6,"P")</f>
@@ -1691,41 +1750,41 @@
         <f aca="false">COUNTIF(V6:AG6,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="9" t="n">
+      <c r="AM6" s="10" t="n">
         <f aca="false">ROUND((AJ6+AK6/2+AL6/4)*10/8,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P7" s="1" t="n">
         <f aca="false">COUNTIF(E7:N7,"P")</f>
@@ -1752,31 +1811,31 @@
         <v>8</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI7" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ7" s="3" t="n">
         <f aca="false">COUNTIF(V7:AG7,"P")</f>
@@ -1790,49 +1849,49 @@
         <f aca="false">COUNTIF(V7:AG7,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="9" t="n">
+      <c r="AM7" s="10" t="n">
         <f aca="false">ROUND((AJ7+AK7/2+AL7/4)*10/8,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0.638888888888889</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="J8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.638888888888889</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="8" t="n">
         <v>0.604166666666667</v>
       </c>
       <c r="P8" s="1" t="n">
@@ -1860,43 +1919,43 @@
         <v>7</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W8" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" s="8" t="n">
         <v>0.625</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z8" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z8" s="8" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB8" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB8" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD8" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI8" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <f aca="false">COUNTIF(V8:AG8,"P")</f>
@@ -1910,44 +1969,44 @@
         <f aca="false">COUNTIF(V8:AG8,"T")</f>
         <v>2</v>
       </c>
-      <c r="AM8" s="9" t="n">
+      <c r="AM8" s="10" t="n">
         <f aca="false">ROUND((AJ8+AK8/2+AL8/4)*10/8,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="8" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P9" s="1" t="n">
         <f aca="false">COUNTIF(E9:N9,"P")</f>
@@ -1974,31 +2033,31 @@
         <v>3</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI9" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ9" s="3" t="n">
         <f aca="false">COUNTIF(V9:AG9,"P")</f>
@@ -2012,45 +2071,45 @@
         <f aca="false">COUNTIF(V9:AG9,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="9" t="n">
+      <c r="AM9" s="10" t="n">
         <f aca="false">ROUND((AJ9+AK9/2+AL9/4)*10/8,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="11" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="2" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="n">
@@ -2078,40 +2137,40 @@
         <v>10</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W10" s="1"/>
       <c r="X10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB10" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB10" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE10" s="1"/>
       <c r="AF10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AH10" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="AI10" s="8" t="s">
-        <v>20</v>
+      <c r="AI10" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <f aca="false">COUNTIF(V10:AG10,"P")</f>
@@ -2125,50 +2184,50 @@
         <f aca="false">COUNTIF(V10:AG10,"T")</f>
         <v>2</v>
       </c>
-      <c r="AM10" s="9" t="n">
+      <c r="AM10" s="10" t="n">
         <f aca="false">ROUND((AJ10+AK10/2+AL10/4)*10/8,0)</f>
         <v>3</v>
       </c>
-      <c r="AN10" s="0"/>
-      <c r="AO10" s="0"/>
-      <c r="AP10" s="0"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="1"/>
+      <c r="AP10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.625</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2" t="n">
@@ -2191,194 +2250,207 @@
         <f aca="false">ROUND(P11+Q11+R11/2,0)</f>
         <v>4</v>
       </c>
-      <c r="U11" s="12" t="n">
+      <c r="U11" s="13" t="n">
         <f aca="false">ROUND(T11*10/$W$1,0)</f>
         <v>7</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="2"/>
       <c r="AC11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD11" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="AE11" s="2"/>
-      <c r="AF11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" s="10" t="s">
-        <v>19</v>
+      <c r="AF11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG11" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="AH11" s="2"/>
-      <c r="AI11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ11" s="10" t="n">
+      <c r="AI11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ11" s="11" t="n">
         <f aca="false">COUNTIF(V11:AG11,"P")</f>
         <v>8</v>
       </c>
-      <c r="AK11" s="10" t="n">
+      <c r="AK11" s="11" t="n">
         <f aca="false">COUNTIF(V11:AG11,"M")</f>
         <v>0</v>
       </c>
-      <c r="AL11" s="10" t="n">
+      <c r="AL11" s="11" t="n">
         <f aca="false">COUNTIF(V11:AG11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="13" t="n">
+      <c r="AM11" s="14" t="n">
         <f aca="false">ROUND((AJ11+AK11/2+AL11/4)*10/8,0)</f>
         <v>10</v>
       </c>
-      <c r="AN11" s="11"/>
-      <c r="AO11" s="11"/>
-      <c r="AP11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="AN11" s="2"/>
+      <c r="AO11" s="2"/>
+      <c r="AP11" s="2"/>
+    </row>
+    <row r="12" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P12" s="1" t="n">
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="n">
         <f aca="false">COUNTIF(E12:N12,"P")</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="Q12" s="2" t="n">
         <f aca="false">COUNTIF(E12:N12,"C")</f>
         <v>0</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="R12" s="2" t="n">
         <f aca="false">COUNTIF(E12:N12,"M")</f>
         <v>0</v>
       </c>
-      <c r="S12" s="1" t="n">
+      <c r="S12" s="2" t="n">
         <f aca="false">COUNTIF(E12:N12,"T")</f>
         <v>0</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="T12" s="2" t="n">
         <f aca="false">ROUND(P12+Q12+R12/2,0)</f>
         <v>0</v>
       </c>
-      <c r="U12" s="5" t="n">
+      <c r="U12" s="13" t="n">
         <f aca="false">ROUND(T12*10/$W$1,0)</f>
         <v>0</v>
       </c>
-      <c r="V12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ12" s="3" t="n">
+      <c r="V12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH12" s="2"/>
+      <c r="AI12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ12" s="11" t="n">
         <f aca="false">COUNTIF(V12:AG12,"P")</f>
         <v>0</v>
       </c>
-      <c r="AK12" s="3" t="n">
+      <c r="AK12" s="11" t="n">
         <f aca="false">COUNTIF(V12:AG12,"M")</f>
         <v>0</v>
       </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AL12" s="11" t="n">
         <f aca="false">COUNTIF(V12:AG12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="9" t="n">
+      <c r="AM12" s="14" t="n">
         <f aca="false">ROUND((AJ12+AK12/2+AL12/4)*10/8,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AN12" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P13" s="1" t="n">
         <f aca="false">COUNTIF(E13:N13,"P")</f>
@@ -2405,34 +2477,34 @@
         <v>8</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD13" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI13" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="AI13" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <f aca="false">COUNTIF(V13:AG13,"P")</f>
@@ -2446,41 +2518,41 @@
         <f aca="false">COUNTIF(V13:AG13,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="9" t="n">
+      <c r="AM13" s="10" t="n">
         <f aca="false">ROUND((AJ13+AK13/2+AL13/4)*10/8,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P14" s="1" t="n">
         <f aca="false">COUNTIF(E14:N14,"P")</f>
@@ -2507,34 +2579,34 @@
         <v>7</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z14" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" s="8" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI14" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="AI14" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <f aca="false">COUNTIF(V14:AG14,"P")</f>
@@ -2548,41 +2620,41 @@
         <f aca="false">COUNTIF(V14:AG14,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="9" t="n">
+      <c r="AM14" s="10" t="n">
         <f aca="false">ROUND((AJ14+AK14/2+AL14/4)*10/8,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P15" s="1" t="n">
         <f aca="false">COUNTIF(E15:N15,"P")</f>
@@ -2609,34 +2681,34 @@
         <v>3</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Y15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AB15" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD15" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI15" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="AI15" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <f aca="false">COUNTIF(V15:AG15,"P")</f>
@@ -2650,43 +2722,43 @@
         <f aca="false">COUNTIF(V15:AG15,"T")</f>
         <v>1</v>
       </c>
-      <c r="AM15" s="9" t="n">
+      <c r="AM15" s="10" t="n">
         <f aca="false">ROUND((AJ15+AK15/2+AL15/4)*10/8,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="P16" s="1" t="n">
@@ -2714,34 +2786,34 @@
         <v>7</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z16" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z16" s="8" t="n">
         <v>0.638888888888889</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD16" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI16" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="AI16" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <f aca="false">COUNTIF(V16:AG16,"P")</f>
@@ -2755,7 +2827,7 @@
         <f aca="false">COUNTIF(V16:AG16,"T")</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="9" t="n">
+      <c r="AM16" s="10" t="n">
         <f aca="false">ROUND((AJ16+AK16/2+AL16/4)*10/8,0)</f>
         <v>5</v>
       </c>
@@ -2826,10 +2898,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G18" s="1" t="n">
         <f aca="false">COUNTIF(G3:G16,"T")</f>
@@ -2907,7 +2979,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD20" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD16,"o")</f>
@@ -2924,7 +2996,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V21" s="1" t="n">
         <f aca="false">SUM(V17:V19)</f>
@@ -3001,19 +3073,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -3035,16 +3107,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -3063,13 +3135,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>5</v>
@@ -3077,13 +3149,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>5</v>
@@ -3091,13 +3163,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>4</v>
@@ -3105,13 +3177,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3</v>
@@ -3119,13 +3191,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
@@ -3133,13 +3205,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -3150,7 +3222,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1</v>
@@ -3164,16 +3236,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8</v>
@@ -3187,16 +3259,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -3210,16 +3282,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -3233,16 +3305,16 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -3256,16 +3328,16 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -3279,7 +3351,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -3293,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -3307,16 +3379,16 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -3335,13 +3407,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -3349,13 +3421,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>6</v>
@@ -3363,13 +3435,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
@@ -3380,16 +3452,16 @@
         <v>12</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -3403,16 +3475,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -3426,27 +3498,27 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H25" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I25" s="1" t="n">
         <f aca="false">COUNTIF(I2:I24,"&gt;0")</f>
@@ -3469,7 +3541,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr defaultColWidth="9.61328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -3490,101 +3562,116 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="T1" s="4" t="n">
         <v>45877</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="Y1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AE1" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF1" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="18" t="n">
         <v>45855</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="20" t="n">
         <v>45821</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="16" t="n">
+      <c r="H2" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="I2" s="17" t="n">
+      <c r="I2" s="20" t="n">
         <v>45849</v>
       </c>
       <c r="J2" s="1" t="n">
@@ -3602,7 +3689,7 @@
         <f aca="false">IF(L2&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="N2" s="14" t="n">
+      <c r="N2" s="17" t="n">
         <v>3</v>
       </c>
       <c r="O2" s="1" t="n">
@@ -3617,7 +3704,7 @@
       <c r="R2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S2" s="9" t="n">
+      <c r="S2" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N2:O2,L2),0)</f>
         <v>7</v>
       </c>
@@ -3627,30 +3714,32 @@
       <c r="V2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W2" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="W2" s="1"/>
       <c r="X2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Y2" s="1" t="n">
+      <c r="AA2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Z2" s="1" t="n">
-        <f aca="false">X2+Y2/2</f>
+      <c r="AB2" s="1" t="n">
+        <f aca="false">Z2+AA2/2</f>
         <v>5.5</v>
       </c>
-      <c r="AA2" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V2:W2,Z2),0)&gt;10,10,ROUND(AVERAGE(V2:W2,Z2),0))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC2" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V2:X2,AB2),0)&gt;10,10,ROUND(AVERAGE(V2:X2,AB2),0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>7</v>
@@ -3694,7 +3783,7 @@
       <c r="R3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S3" s="9" t="n">
+      <c r="S3" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N3:O3,L3),0)</f>
         <v>8</v>
       </c>
@@ -3704,121 +3793,143 @@
       <c r="V3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W3" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="W3" s="1"/>
       <c r="X3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Z3" s="1" t="n">
-        <f aca="false">X3+Y3/2</f>
+      <c r="AB3" s="1" t="n">
+        <f aca="false">Z3+AA3/2</f>
         <v>11.5</v>
       </c>
-      <c r="AA3" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V3:W3,Z3),0)&gt;10,10,ROUND(AVERAGE(V3:W3,Z3),0))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="AC3" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V3:X3,AB3),0)&gt;10,10,ROUND(AVERAGE(V3:X3,AB3),0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="15" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="n">
+      <c r="B4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <f aca="false">H4+J4/2</f>
         <v>8</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,K4),0)</f>
         <v>3</v>
       </c>
-      <c r="M4" s="1" t="str">
+      <c r="M4" s="2" t="str">
         <f aca="false">IF(L4&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="N4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="9" t="n">
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(N4:O4,L4),0)</f>
         <v>1</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="1" t="n">
-        <f aca="false">X4+Y4/2</f>
-        <v>0</v>
-      </c>
-      <c r="AA4" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V4:W4,Z4),0)&gt;10,10,ROUND(AVERAGE(V4:W4,Z4),0))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" s="21" t="n">
+        <v>45996</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="21" t="n">
+        <v>45996</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <f aca="false">Z4+AA4/2</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V4:X4,AB4),0)&gt;10,10,ROUND(AVERAGE(V4:X4,AB4),0))</f>
+        <v>10</v>
+      </c>
+      <c r="AD4" s="15" t="n">
+        <f aca="false">AVERAGE(V4,X4)</f>
+        <v>10</v>
+      </c>
+      <c r="AE4" s="22" t="n">
+        <f aca="false">ROUND(AD4*6/10,0)</f>
+        <v>6</v>
+      </c>
+      <c r="AF4" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="18" t="n">
         <v>45887</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="18" t="n">
         <v>45856</v>
       </c>
       <c r="G5" s="1" t="n">
@@ -3857,7 +3968,7 @@
       <c r="R5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N5:O5,L5),0)</f>
         <v>7</v>
       </c>
@@ -3867,30 +3978,32 @@
       <c r="V5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W5" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="W5" s="1"/>
       <c r="X5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="AA5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Z5" s="1" t="n">
-        <f aca="false">X5+Y5/2</f>
+      <c r="AB5" s="1" t="n">
+        <f aca="false">Z5+AA5/2</f>
         <v>5.5</v>
       </c>
-      <c r="AA5" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V5:W5,Z5),0)&gt;10,10,ROUND(AVERAGE(V5:W5,Z5),0))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC5" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V5:X5,AB5),0)&gt;10,10,ROUND(AVERAGE(V5:X5,AB5),0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>8</v>
@@ -3934,7 +4047,7 @@
       <c r="R6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N6:O6,L6),0)</f>
         <v>8</v>
       </c>
@@ -3944,30 +4057,32 @@
       <c r="V6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="W6" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="W6" s="1"/>
       <c r="X6" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y6" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Y6" s="1"/>
       <c r="Z6" s="1" t="n">
-        <f aca="false">X6+Y6/2</f>
+        <v>8</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <f aca="false">Z6+AA6/2</f>
         <v>8.5</v>
       </c>
-      <c r="AA6" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V6:W6,Z6),0)&gt;10,10,ROUND(AVERAGE(V6:W6,Z6),0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC6" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V6:X6,AB6),0)&gt;10,10,ROUND(AVERAGE(V6:X6,AB6),0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>10</v>
@@ -4011,7 +4126,7 @@
       <c r="R7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N7:O7,L7),0)</f>
         <v>9</v>
       </c>
@@ -4021,30 +4136,32 @@
       <c r="V7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W7" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="W7" s="1"/>
       <c r="X7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Y7" s="1" t="n">
+      <c r="AA7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="Z7" s="1" t="n">
-        <f aca="false">X7+Y7/2</f>
+      <c r="AB7" s="1" t="n">
+        <f aca="false">Z7+AA7/2</f>
         <v>34</v>
       </c>
-      <c r="AA7" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V7:W7,Z7),0)&gt;10,10,ROUND(AVERAGE(V7:W7,Z7),0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC7" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V7:X7,AB7),0)&gt;10,10,ROUND(AVERAGE(V7:X7,AB7),0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>1</v>
@@ -4088,12 +4205,12 @@
       <c r="R8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N8:O8,L8),0)</f>
         <v>5</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U8" s="1" t="n">
         <v>1</v>
@@ -4101,30 +4218,32 @@
       <c r="V8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W8" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="W8" s="1"/>
       <c r="X8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z8" s="1" t="n">
-        <f aca="false">X8+Y8/2</f>
+      <c r="AB8" s="1" t="n">
+        <f aca="false">Z8+AA8/2</f>
         <v>5.5</v>
       </c>
-      <c r="AA8" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V8:W8,Z8),0)&gt;10,10,ROUND(AVERAGE(V8:W8,Z8),0))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC8" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V8:X8,AB8),0)&gt;10,10,ROUND(AVERAGE(V8:X8,AB8),0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>7</v>
@@ -4168,7 +4287,7 @@
       <c r="R9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S9" s="9" t="n">
+      <c r="S9" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N9:O9,L9),0)</f>
         <v>9</v>
       </c>
@@ -4178,30 +4297,32 @@
       <c r="V9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W9" s="1" t="n">
-        <v>3</v>
-      </c>
+      <c r="W9" s="1"/>
       <c r="X9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="Z9" s="1" t="n">
-        <f aca="false">X9+Y9/2</f>
+      <c r="AB9" s="1" t="n">
+        <f aca="false">Z9+AA9/2</f>
         <v>15.5</v>
       </c>
-      <c r="AA9" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V9:W9,Z9),0)&gt;10,10,ROUND(AVERAGE(V9:W9,Z9),0))</f>
+      <c r="AC9" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V9:X9,AB9),0)&gt;10,10,ROUND(AVERAGE(V9:X9,AB9),0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>8</v>
@@ -4212,10 +4333,10 @@
       <c r="G10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="18" t="n">
         <v>45855</v>
       </c>
       <c r="J10" s="1" t="n">
@@ -4233,7 +4354,7 @@
         <f aca="false">IF(L10&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="N10" s="14" t="n">
+      <c r="N10" s="17" t="n">
         <v>5</v>
       </c>
       <c r="O10" s="1" t="n">
@@ -4248,7 +4369,7 @@
       <c r="R10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N10:O10,L10),0)</f>
         <v>7</v>
       </c>
@@ -4258,110 +4379,125 @@
       <c r="V10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W10" s="1" t="n">
-        <v>8</v>
-      </c>
+      <c r="W10" s="1"/>
       <c r="X10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y10" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Y10" s="1"/>
       <c r="Z10" s="1" t="n">
-        <f aca="false">X10+Y10/2</f>
+        <v>10</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <f aca="false">Z10+AA10/2</f>
         <v>10.5</v>
       </c>
-      <c r="AA10" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V10:W10,Z10),0)&gt;10,10,ROUND(AVERAGE(V10:W10,Z10),0))</f>
+      <c r="AC10" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V10:X10,AB10),0)&gt;10,10,ROUND(AVERAGE(V10:X10,AB10),0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1" t="n">
+    <row r="11" s="15" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
         <f aca="false">H11+J11/2</f>
         <v>1</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="L11" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,K11),0)</f>
         <v>1</v>
       </c>
-      <c r="M11" s="1" t="str">
+      <c r="M11" s="2" t="str">
         <f aca="false">IF(L11&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1" t="n">
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="Q11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="R11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(N11:O11,L11),0)</f>
         <v>1</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="1" t="n">
-        <f aca="false">X11+Y11/2</f>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V11:W11,Z11),0)&gt;10,10,ROUND(AVERAGE(V11:W11,Z11),0))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="T11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <f aca="false">Z11+AA11/2</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="14" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V11:X11,AB11),0)&gt;10,10,ROUND(AVERAGE(V11:X11,AB11),0))</f>
+        <v>1</v>
+      </c>
+      <c r="AD11" s="15" t="n">
+        <f aca="false">AVERAGE(V11,X11)</f>
+        <v>1</v>
+      </c>
+      <c r="AE11" s="22" t="n">
+        <f aca="false">ROUND(AD11*7/10,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>9</v>
@@ -4405,7 +4541,7 @@
       <c r="R12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N12:O12,L12),0)</f>
         <v>8</v>
       </c>
@@ -4415,38 +4551,40 @@
       <c r="V12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="W12" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="W12" s="1"/>
       <c r="X12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="Z12" s="1" t="n">
-        <f aca="false">X12+Y12/2</f>
+      <c r="AB12" s="1" t="n">
+        <f aca="false">Z12+AA12/2</f>
         <v>39.5</v>
       </c>
-      <c r="AA12" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V12:W12,Z12),0)&gt;10,10,ROUND(AVERAGE(V12:W12,Z12),0))</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC12" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V12:X12,AB12),0)&gt;10,10,ROUND(AVERAGE(V12:X12,AB12),0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="20" t="n">
         <v>45821</v>
       </c>
       <c r="G13" s="1" t="n">
@@ -4485,7 +4623,7 @@
       <c r="R13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N13:O13,L13),0)</f>
         <v>7</v>
       </c>
@@ -4495,30 +4633,32 @@
       <c r="V13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W13" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="W13" s="1"/>
       <c r="X13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Y13" s="1" t="n">
+      <c r="AA13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="Z13" s="1" t="n">
-        <f aca="false">X13+Y13/2</f>
+      <c r="AB13" s="1" t="n">
+        <f aca="false">Z13+AA13/2</f>
         <v>9.5</v>
       </c>
-      <c r="AA13" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V13:W13,Z13),0)&gt;10,10,ROUND(AVERAGE(V13:W13,Z13),0))</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC13" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V13:X13,AB13),0)&gt;10,10,ROUND(AVERAGE(V13:X13,AB13),0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>8</v>
@@ -4568,7 +4708,7 @@
       <c r="R14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N14:O14,L14),0)</f>
         <v>7</v>
       </c>
@@ -4578,30 +4718,32 @@
       <c r="V14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W14" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="W14" s="1"/>
       <c r="X14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Y14" s="1" t="n">
+      <c r="AA14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Z14" s="1" t="n">
-        <f aca="false">X14+Y14/2</f>
+      <c r="AB14" s="1" t="n">
+        <f aca="false">Z14+AA14/2</f>
         <v>6</v>
       </c>
-      <c r="AA14" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V14:W14,Z14),0)&gt;10,10,ROUND(AVERAGE(V14:W14,Z14),0))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AC14" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V14:X14,AB14),0)&gt;10,10,ROUND(AVERAGE(V14:X14,AB14),0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>10</v>
@@ -4612,10 +4754,10 @@
       <c r="G15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="15" t="n">
+      <c r="H15" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="18" t="n">
         <v>45856</v>
       </c>
       <c r="J15" s="1" t="n">
@@ -4648,7 +4790,7 @@
       <c r="R15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(N15:O15,L15),0)</f>
         <v>9</v>
       </c>
@@ -4658,21 +4800,23 @@
       <c r="V15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="W15" s="1" t="n">
-        <v>7</v>
-      </c>
+      <c r="W15" s="1"/>
       <c r="X15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Y15" s="1" t="n">
+      <c r="AA15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Z15" s="1" t="n">
-        <f aca="false">X15+Y15/2</f>
-        <v>7</v>
-      </c>
-      <c r="AA15" s="9" t="n">
-        <f aca="false">IF(ROUND(AVERAGE(V15:W15,Z15),0)&gt;10,10,ROUND(AVERAGE(V15:W15,Z15),0))</f>
+      <c r="AB15" s="1" t="n">
+        <f aca="false">Z15+AA15/2</f>
+        <v>7</v>
+      </c>
+      <c r="AC15" s="10" t="n">
+        <f aca="false">IF(ROUND(AVERAGE(V15:X15,AB15),0)&gt;10,10,ROUND(AVERAGE(V15:X15,AB15),0))</f>
         <v>8</v>
       </c>
     </row>
@@ -4689,7 +4833,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA15">
+  <conditionalFormatting sqref="AC2:AC15">
     <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -4698,6 +4842,14 @@
       <formula>6</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE4:AE11">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4740,7 +4892,7 @@
         <v>45751</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4748,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K2" s="1" t="n">
         <f aca="false">I2+J2</f>
@@ -4760,7 +4912,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>2</v>
@@ -4778,7 +4930,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">I4+J4</f>
@@ -4790,7 +4942,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="n">
         <f aca="false">I5+J5</f>
@@ -4802,7 +4954,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>1</v>
@@ -4817,9 +4969,9 @@
         <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>60</v>
       </c>
       <c r="K7" s="1" t="n">
@@ -4833,7 +4985,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>2</v>
@@ -4848,7 +5000,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>4</v>
@@ -4867,7 +5019,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>1</v>
@@ -4882,7 +5034,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K11" s="1" t="n">
         <f aca="false">I11+J11</f>
@@ -4894,7 +5046,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>2</v>
@@ -4913,12 +5065,12 @@
         <v>12</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K13" s="1" t="n">
@@ -4931,7 +5083,7 @@
         <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K14" s="1" t="n">
         <f aca="false">I14+J14</f>
@@ -4943,7 +5095,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>4</v>
@@ -4955,7 +5107,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" s="1" t="n">
         <f aca="false">COUNTIF(I2:I15,"&gt;0")</f>
@@ -4995,13 +5147,13 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -5020,16 +5172,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7</v>
@@ -5040,7 +5192,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -5051,7 +5203,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>1</v>
@@ -5062,16 +5214,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -5082,16 +5234,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -5102,7 +5254,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -5113,16 +5265,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7</v>
@@ -5133,16 +5285,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -5153,7 +5305,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -5164,16 +5316,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>9</v>
@@ -5184,7 +5336,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>1</v>
@@ -5195,7 +5347,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -5206,16 +5358,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -5252,22 +5404,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5275,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -5289,16 +5441,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -5317,13 +5469,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -5331,13 +5483,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -5345,13 +5497,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>6</v>
@@ -5359,13 +5511,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>4</v>
@@ -5376,7 +5528,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
@@ -5390,7 +5542,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -5404,16 +5556,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -5427,16 +5579,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>9</v>
@@ -5450,7 +5602,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -5464,16 +5616,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -5492,13 +5644,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>5</v>
@@ -5509,16 +5661,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -5532,7 +5684,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -5546,16 +5698,16 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -5574,13 +5726,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>5</v>
@@ -5591,7 +5743,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -5605,7 +5757,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -5619,16 +5771,16 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -5666,51 +5818,51 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -5774,22 +5926,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5797,16 +5949,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -5820,16 +5972,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -5848,13 +6000,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -5865,7 +6017,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -5879,16 +6031,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -5902,16 +6054,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -5930,13 +6082,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>8</v>
@@ -5947,16 +6099,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -5975,13 +6127,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -5989,13 +6141,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>4</v>
@@ -6006,16 +6158,16 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -6034,13 +6186,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -6048,13 +6200,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>1</v>
@@ -6065,16 +6217,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -6093,13 +6245,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -6107,13 +6259,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>3</v>
@@ -6124,16 +6276,16 @@
         <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -6152,13 +6304,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>7</v>
@@ -6169,7 +6321,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -6183,16 +6335,16 @@
         <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -6211,13 +6363,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>7</v>
@@ -6228,16 +6380,16 @@
         <v>12</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -6256,13 +6408,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -6273,16 +6425,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -6296,16 +6448,16 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -6353,22 +6505,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6376,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -6390,16 +6542,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -6418,13 +6570,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -6435,16 +6587,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -6458,16 +6610,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -6481,16 +6633,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -6504,16 +6656,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -6527,7 +6679,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -6541,16 +6693,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -6564,7 +6716,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -6578,7 +6730,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -6592,16 +6744,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -6615,16 +6767,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -6638,16 +6790,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -6661,7 +6813,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -6709,51 +6861,51 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
